--- a/temp/espc-2/searchByMAC-7.xlsx
+++ b/temp/espc-2/searchByMAC-7.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="42">
   <si>
     <t>ЭСПЦ-2</t>
   </si>
@@ -134,6 +134,12 @@
   </si>
   <si>
     <t>17.48</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
@@ -516,15 +522,21 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
+      <c r="N2" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>

--- a/temp/espc-2/searchByMAC-7.xlsx
+++ b/temp/espc-2/searchByMAC-7.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="48">
   <si>
     <t>ЭСПЦ-2</t>
   </si>
@@ -140,6 +140,24 @@
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>6.2.17</t>
+  </si>
+  <si>
+    <t>6.2.16</t>
+  </si>
+  <si>
+    <t>6.2.23</t>
+  </si>
+  <si>
+    <t>6.2.22</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -490,13 +508,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB211"/>
+  <dimension ref="A1:AD211"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="44" width="5.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -516,7 +534,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -540,7 +558,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>1</v>
@@ -560,7 +578,7 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
@@ -578,11 +596,14 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N4">
+        <v>13</v>
+      </c>
+      <c r="W4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
@@ -600,11 +621,22 @@
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q5" s="1"/>
+      <c r="X5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z5" s="1"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
@@ -622,11 +654,22 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q6" s="1"/>
+      <c r="X6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z6" s="1"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
@@ -644,11 +687,22 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q7" s="1"/>
+      <c r="X7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z7" s="1"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
@@ -666,11 +720,22 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q8" s="1"/>
+      <c r="X8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z8" s="1"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
@@ -688,11 +753,22 @@
       <c r="K9" s="2"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q9" s="1"/>
+      <c r="X9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z9" s="1"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
@@ -710,11 +786,32 @@
       <c r="K10" s="2"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N10">
+        <v>11</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W10">
+        <v>11</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
@@ -732,11 +829,26 @@
       <c r="K11" s="2"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z11" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
@@ -754,11 +866,38 @@
       <c r="K12" s="2"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="W12">
+        <v>1</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA12" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
@@ -776,11 +915,38 @@
       <c r="K13" s="2"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W13">
+        <v>1</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA13" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
@@ -798,11 +964,38 @@
       <c r="K14" s="2"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N14">
+        <v>11</v>
+      </c>
+      <c r="O14" s="1">
+        <v>6</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W14">
+        <v>11</v>
+      </c>
+      <c r="X14" s="1">
+        <v>6</v>
+      </c>
+      <c r="Y14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA14" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
@@ -820,11 +1013,38 @@
       <c r="K15" s="2"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15" s="1">
+        <v>13</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W15">
+        <v>1</v>
+      </c>
+      <c r="X15" s="1">
+        <v>13</v>
+      </c>
+      <c r="Y15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
@@ -842,11 +1062,32 @@
       <c r="K16" s="2"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="W16">
+        <v>1</v>
+      </c>
+      <c r="X16" s="1">
+        <v>14</v>
+      </c>
+      <c r="Y16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA16" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -860,11 +1101,38 @@
       <c r="K17" s="2"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB17" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
         <v>8</v>
@@ -880,11 +1148,44 @@
       <c r="K18" s="2"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="W18">
+        <v>1</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB18" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
@@ -902,11 +1203,50 @@
       <c r="K19" s="2"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N19">
+        <v>11</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W19">
+        <v>11</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC19" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
@@ -924,11 +1264,50 @@
       <c r="K20" s="2"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
@@ -946,11 +1325,56 @@
       <c r="K21" s="2"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="W21">
+        <v>1</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD21" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1" t="s">
@@ -968,11 +1392,56 @@
       <c r="K22" s="2"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD22" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
@@ -990,11 +1459,8 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
@@ -1012,11 +1478,14 @@
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N24">
+        <v>13</v>
+      </c>
+      <c r="W24">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
@@ -1034,11 +1503,22 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q25" s="1"/>
+      <c r="X25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z25" s="1"/>
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
@@ -1056,11 +1536,22 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q26" s="1"/>
+      <c r="X26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z26" s="1"/>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
@@ -1078,11 +1569,22 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q27" s="1"/>
+      <c r="X27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y27" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z27" s="1"/>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1" t="s">
@@ -1100,11 +1602,22 @@
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q28" s="1"/>
+      <c r="X28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z28" s="1"/>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
@@ -1122,11 +1635,18 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O29" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q29" s="1"/>
+      <c r="X29" s="1"/>
+      <c r="Y29" s="1"/>
+      <c r="Z29" s="1"/>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
@@ -1144,11 +1664,14 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q30" s="1"/>
+      <c r="X30" s="1"/>
+      <c r="Y30" s="1"/>
+      <c r="Z30" s="1"/>
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
@@ -1166,11 +1689,20 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1"/>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1184,11 +1716,16 @@
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1"/>
+      <c r="AA32" s="1"/>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
         <v>17</v>
@@ -1208,11 +1745,14 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="Y33" s="1"/>
+      <c r="Z33" s="1"/>
+      <c r="AA33" s="1"/>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1" t="s">
@@ -1238,11 +1778,20 @@
         <v>19</v>
       </c>
       <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="P34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y34" s="1"/>
+      <c r="Z34" s="1"/>
+      <c r="AA34" s="1"/>
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1" t="s">
@@ -1272,7 +1821,7 @@
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
@@ -1302,7 +1851,7 @@
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1" t="s">
@@ -1324,7 +1873,7 @@
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1" t="s">
@@ -1350,7 +1899,7 @@
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1" t="s">
@@ -1380,7 +1929,7 @@
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1" t="s">
@@ -1402,7 +1951,7 @@
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1" t="s">
@@ -1424,7 +1973,7 @@
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1" t="s">
@@ -1454,7 +2003,7 @@
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1" t="s">
@@ -1480,7 +2029,7 @@
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1" t="s">
@@ -1502,7 +2051,7 @@
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1" t="s">
@@ -1524,7 +2073,7 @@
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1" t="s">
@@ -1554,7 +2103,7 @@
       <c r="O46" s="2"/>
       <c r="P46" s="2"/>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -1572,7 +2121,7 @@
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
         <v>16</v>

--- a/temp/espc-2/searchByMAC-7.xlsx
+++ b/temp/espc-2/searchByMAC-7.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="48">
   <si>
     <t>ЭСПЦ-2</t>
   </si>
@@ -838,6 +838,9 @@
       <c r="Q11" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="W11">
+        <v>11</v>
+      </c>
       <c r="X11" s="1" t="s">
         <v>8</v>
       </c>
@@ -1101,6 +1104,9 @@
       <c r="K17" s="2"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
+      <c r="N17">
+        <v>11</v>
+      </c>
       <c r="O17" s="1" t="s">
         <v>14</v>
       </c>
@@ -1115,6 +1121,9 @@
       </c>
       <c r="S17" s="1" t="s">
         <v>24</v>
+      </c>
+      <c r="W17">
+        <v>11</v>
       </c>
       <c r="X17" s="1" t="s">
         <v>14</v>
@@ -1510,12 +1519,8 @@
         <v>43</v>
       </c>
       <c r="Q25" s="1"/>
-      <c r="X25" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y25" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="X25" s="1"/>
+      <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
